--- a/Result/profitability/4119.xlsx
+++ b/Result/profitability/4119.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.34</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75</v>
+        <v>0.3375</v>
       </c>
       <c r="N2" t="n">
-        <v>26.5625</v>
+        <v>25.6175</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,10 +690,10 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>1.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="N3" t="n">
-        <v>27.0675</v>
+        <v>26.63125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6125</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>28.575</v>
+        <v>28.3425</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>0.76</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6737500000000001</v>
+        <v>0.6362500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>29.27</v>
+        <v>28.2875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0.85</v>
+        <v>0.82125</v>
       </c>
       <c r="N6" t="n">
-        <v>30.53</v>
+        <v>29.71125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>0.9</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9475</v>
+        <v>0.8925000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>32.25375</v>
+        <v>31.265</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03125</v>
+        <v>0.9962500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>33.37875</v>
+        <v>33.15375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>273</v>
+      </c>
+      <c r="D75" t="n">
+        <v>218</v>
+      </c>
+      <c r="E75" t="n">
+        <v>55</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5687500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.73875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.647058823529412</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.800000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08215426745778187</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.578947368421053</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.859999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2810153736145871</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
